--- a/planilhasParaCruzamento/cruzamento-2026-07-02 (bonito).xlsx
+++ b/planilhasParaCruzamento/cruzamento-2026-07-02 (bonito).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70BAB17-7734-4CA0-A124-4D5E1E0DDECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE737A38-1D9C-448E-B14E-E0F4B19EEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="5055" windowWidth="22815" windowHeight="11295" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Vendas Nao Concluidas" sheetId="8" r:id="rId8"/>
     <sheet name="Vendas Canceladas" sheetId="9" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Vendas Nao Concluidas'!$A$1:$AP$1</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26022" uniqueCount="1541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26020" uniqueCount="1541">
   <si>
     <t>Cruzamento de Vendas</t>
   </si>
@@ -4657,7 +4660,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4704,8 +4707,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4745,12 +4754,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4875,9 +4878,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6314,42 +6317,47 @@
   <dimension ref="A1:AO63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="13" customWidth="1"/>
-    <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="21" width="25" customWidth="1"/>
-    <col min="22" max="22" width="18" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="19" customWidth="1"/>
-    <col min="25" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="38" customWidth="1"/>
-    <col min="28" max="30" width="40" customWidth="1"/>
-    <col min="31" max="31" width="28" customWidth="1"/>
-    <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="33" max="33" width="18" customWidth="1"/>
-    <col min="34" max="34" width="14" style="12" customWidth="1"/>
-    <col min="35" max="35" width="21" style="12" customWidth="1"/>
-    <col min="36" max="36" width="22" customWidth="1"/>
-    <col min="37" max="37" width="23" customWidth="1"/>
+    <col min="1" max="1" width="75.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="70.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="62.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="12" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="20" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="39.5703125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="19" customWidth="1"/>
-    <col min="39" max="39" width="21" customWidth="1"/>
-    <col min="40" max="40" width="28" customWidth="1"/>
-    <col min="41" max="41" width="25" customWidth="1"/>
+    <col min="39" max="39" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="58" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="52.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" s="13" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -53696,7 +53704,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:AP262"/>
+  <dimension ref="A1:AP263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -57846,25 +57854,25 @@
       <c r="B33" s="38" t="s">
         <v>429</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="40" t="s">
         <v>430</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="40" t="s">
         <v>431</v>
       </c>
-      <c r="E33" s="38" t="s">
+      <c r="E33" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="38">
+      <c r="F33" s="40">
         <v>1</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="G33" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="I33" s="38" t="s">
+      <c r="I33" s="40" t="s">
         <v>437</v>
       </c>
       <c r="J33" s="21" t="s">
@@ -65264,61 +65272,61 @@
       </c>
     </row>
     <row r="91" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A91" s="39" t="s">
+      <c r="A91" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B91" s="40" t="s">
+      <c r="B91" s="39" t="s">
         <v>1089</v>
       </c>
-      <c r="C91" s="39" t="s">
+      <c r="C91" s="40" t="s">
         <v>1090</v>
       </c>
-      <c r="D91" s="39" t="s">
+      <c r="D91" s="40" t="s">
         <v>1091</v>
       </c>
-      <c r="E91" s="39" t="s">
+      <c r="E91" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="F91" s="39">
+      <c r="F91" s="40">
         <v>1</v>
       </c>
-      <c r="G91" s="39" t="s">
+      <c r="G91" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="H91" s="39" t="s">
+      <c r="H91" s="40" t="s">
         <v>262</v>
       </c>
-      <c r="I91" s="39" t="s">
+      <c r="I91" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="J91" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="K91" s="39" t="s">
+      <c r="J91" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="L91" s="39" t="s">
+      <c r="L91" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="M91" s="39" t="s">
+      <c r="M91" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="N91" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="O91" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="P91" s="39" t="s">
+      <c r="N91" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="O91" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="P91" s="40" t="s">
         <v>478</v>
       </c>
-      <c r="Q91" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="R91" s="39" t="s">
+      <c r="Q91" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="R91" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="S91" s="39" t="s">
+      <c r="S91" s="40" t="s">
         <v>215</v>
       </c>
       <c r="T91" s="21" t="s">
@@ -65395,7 +65403,7 @@
       <c r="A92" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="40" t="s">
+      <c r="B92" s="39" t="s">
         <v>1089</v>
       </c>
       <c r="C92" s="17" t="s">
@@ -65523,7 +65531,7 @@
       <c r="A93" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B93" s="40" t="s">
+      <c r="B93" s="39" t="s">
         <v>1089</v>
       </c>
       <c r="C93" s="21" t="s">
@@ -65651,7 +65659,7 @@
       <c r="A94" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="40" t="s">
+      <c r="B94" s="39" t="s">
         <v>1089</v>
       </c>
       <c r="C94" s="17" t="s">
@@ -65776,7 +65784,7 @@
       </c>
     </row>
     <row r="95" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A95" s="41" t="s">
+      <c r="A95" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B95" s="38" t="s">
@@ -65904,7 +65912,7 @@
       </c>
     </row>
     <row r="96" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A96" s="41" t="s">
+      <c r="A96" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B96" s="38" t="s">
@@ -66032,7 +66040,7 @@
       </c>
     </row>
     <row r="97" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A97" s="41" t="s">
+      <c r="A97" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B97" s="38" t="s">
@@ -66160,7 +66168,7 @@
       </c>
     </row>
     <row r="98" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A98" s="41" t="s">
+      <c r="A98" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B98" s="38" t="s">
@@ -66291,7 +66299,7 @@
       <c r="A99" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B99" s="40" t="s">
+      <c r="B99" s="39" t="s">
         <v>1089</v>
       </c>
       <c r="C99" s="21" t="s">
@@ -66419,7 +66427,7 @@
       <c r="A100" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B100" s="40" t="s">
+      <c r="B100" s="39" t="s">
         <v>1089</v>
       </c>
       <c r="C100" s="17" t="s">
@@ -66547,7 +66555,7 @@
       <c r="A101" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B101" s="40" t="s">
+      <c r="B101" s="39" t="s">
         <v>1089</v>
       </c>
       <c r="C101" s="21" t="s">
@@ -66675,7 +66683,7 @@
       <c r="A102" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B102" s="40" t="s">
+      <c r="B102" s="39" t="s">
         <v>1089</v>
       </c>
       <c r="C102" s="17" t="s">
@@ -68211,7 +68219,7 @@
       <c r="A114" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B114" s="42" t="s">
+      <c r="B114" s="41" t="s">
         <v>700</v>
       </c>
       <c r="C114" s="17" t="s">
@@ -68339,7 +68347,7 @@
       <c r="A115" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B115" s="42" t="s">
+      <c r="B115" s="41" t="s">
         <v>700</v>
       </c>
       <c r="C115" s="21" t="s">
@@ -68467,7 +68475,7 @@
       <c r="A116" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B116" s="42" t="s">
+      <c r="B116" s="41" t="s">
         <v>700</v>
       </c>
       <c r="C116" s="17" t="s">
@@ -68595,7 +68603,7 @@
       <c r="A117" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B117" s="42" t="s">
+      <c r="B117" s="41" t="s">
         <v>700</v>
       </c>
       <c r="C117" s="21" t="s">
@@ -69875,7 +69883,7 @@
       <c r="A127" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B127" s="40" t="s">
+      <c r="B127" s="39" t="s">
         <v>1123</v>
       </c>
       <c r="C127" s="21" t="s">
@@ -70003,11 +70011,11 @@
       <c r="A128" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B128" s="40" t="s">
+      <c r="B128" s="39" t="s">
         <v>1123</v>
       </c>
-      <c r="C128" s="17" t="s">
-        <v>1124</v>
+      <c r="C128" s="17">
+        <v>1996603000158</v>
       </c>
       <c r="D128" s="17" t="s">
         <v>1125</v>
@@ -77555,7 +77563,7 @@
       <c r="A187" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B187" s="43" t="s">
+      <c r="B187" s="42" t="s">
         <v>1234</v>
       </c>
       <c r="C187" s="21" t="s">
@@ -87279,12 +87287,123 @@
         <v>918</v>
       </c>
     </row>
+    <row r="263" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A263" s="36" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B263" s="36" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C263" s="36" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D263" s="36" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E263" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="F263" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="G263" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="H263" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I263" s="36" t="s">
+        <v>397</v>
+      </c>
+      <c r="J263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="K263" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="L263" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="M263" s="36" t="s">
+        <v>644</v>
+      </c>
+      <c r="N263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="O263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="P263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="R263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="S263" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="T263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="U263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="V263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="W263" s="36" t="s">
+        <v>1097</v>
+      </c>
+      <c r="X263" s="36" t="s">
+        <v>1537</v>
+      </c>
+      <c r="Y263" s="36" t="s">
+        <v>1538</v>
+      </c>
+      <c r="Z263" s="36" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AA263" s="36" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AB263" s="36" t="s">
+        <v>1539</v>
+      </c>
+      <c r="AC263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF263" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG263" s="37" t="s">
+        <v>1540</v>
+      </c>
+      <c r="AH263" s="43"/>
+      <c r="AI263" s="43"/>
+      <c r="AJ263" s="43"/>
+      <c r="AK263" s="43"/>
+      <c r="AL263" s="43"/>
+      <c r="AM263" s="43"/>
+      <c r="AN263" s="43"/>
+      <c r="AO263" s="43"/>
+      <c r="AP263" s="43"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP1" xr:uid="{00000000-0009-0000-0000-000007000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AP262">
+  <autoFilter ref="A1:AP1" xr:uid="{00000000-0001-0000-0700-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AP263">
       <sortCondition ref="S1"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
@@ -87292,7 +87411,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AG39"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -90970,11 +91089,11 @@
       <c r="A37" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="42" t="s">
         <v>1234</v>
       </c>
-      <c r="C37" s="36" t="s">
-        <v>1235</v>
+      <c r="C37" s="36">
+        <v>5239386000102</v>
       </c>
       <c r="D37" s="36" t="s">
         <v>1236</v>
@@ -91168,109 +91287,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="36" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>1536</v>
-      </c>
-      <c r="D39" s="36" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E39" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="G39" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="H39" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="I39" s="36" t="s">
-        <v>397</v>
-      </c>
-      <c r="J39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="L39" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="M39" s="36" t="s">
-        <v>644</v>
-      </c>
-      <c r="N39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="O39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="P39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="R39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="S39" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="T39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="U39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="V39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="W39" s="36" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X39" s="36" t="s">
-        <v>1537</v>
-      </c>
-      <c r="Y39" s="36" t="s">
-        <v>1538</v>
-      </c>
-      <c r="Z39" s="36" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AA39" s="36" t="s">
-        <v>1093</v>
-      </c>
-      <c r="AB39" s="36" t="s">
-        <v>1539</v>
-      </c>
-      <c r="AC39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF39" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG39" s="37" t="s">
-        <v>1540</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AG1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/planilhasParaCruzamento/cruzamento-2026-07-02 (bonito).xlsx
+++ b/planilhasParaCruzamento/cruzamento-2026-07-02 (bonito).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE737A38-1D9C-448E-B14E-E0F4B19EEDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A93215-8A37-4CAB-A245-5D2A7646F6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6300" yWindow="2655" windowWidth="22815" windowHeight="12375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo" sheetId="1" r:id="rId1"/>
@@ -5223,9 +5223,9 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.35">
